--- a/HSI_FSC_result/2. Dropout/score_nodropout.xlsx
+++ b/HSI_FSC_result/2. Dropout/score_nodropout.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_2_Dropout\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\2. Dropout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18627B69-5BCF-4FA5-80AC-469DBCB8CE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29364DA2-4E26-43DC-B55F-F7DD39CD5B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="2940" windowWidth="21600" windowHeight="12885" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
-    <sheet name="SA" sheetId="2" r:id="rId2"/>
-    <sheet name="UP" sheetId="3" r:id="rId3"/>
+    <sheet name="UP" sheetId="3" r:id="rId2"/>
+    <sheet name="SA" sheetId="2" r:id="rId3"/>
     <sheet name="XZ" sheetId="5" r:id="rId4"/>
     <sheet name="PC" sheetId="4" r:id="rId5"/>
   </sheets>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -102,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -381,9 +388,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>50.588237999999997</v>
       </c>
@@ -419,7 +426,7 @@
         <v>41.980216099999993</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>50.560116000000001</v>
       </c>
@@ -455,7 +462,7 @@
         <v>50.659742600000001</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>31.849913000000001</v>
       </c>
@@ -491,7 +498,7 @@
         <v>39.071570399999999</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>48.283259999999999</v>
       </c>
@@ -527,7 +534,7 @@
         <v>51.397495300000003</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>94.328354000000004</v>
       </c>
@@ -563,7 +570,7 @@
         <v>63.469282699999994</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>81.724590000000006</v>
       </c>
@@ -599,7 +606,7 @@
         <v>74.400935599999997</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>49.122807000000002</v>
       </c>
@@ -635,7 +642,7 @@
         <v>39.312124300000008</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>94.082840000000004</v>
       </c>
@@ -671,7 +678,7 @@
         <v>94.7728465</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>33.333336000000003</v>
       </c>
@@ -707,7 +714,7 @@
         <v>23.618907400000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>32.871535999999999</v>
       </c>
@@ -743,7 +750,7 @@
         <v>43.904120399999996</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>46.159419999999997</v>
       </c>
@@ -779,7 +786,7 @@
         <v>68.417326000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>68.481849999999994</v>
       </c>
@@ -815,7 +822,7 @@
         <v>45.637134500000009</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>78.125</v>
       </c>
@@ -851,7 +858,7 @@
         <v>70.9173136</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>94.776750000000007</v>
       </c>
@@ -887,7 +894,7 @@
         <v>89.643370599999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>69.189189999999996</v>
       </c>
@@ -923,7 +930,7 @@
         <v>57.8374588</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>89.898994000000002</v>
       </c>
@@ -959,7 +966,7 @@
         <v>69.485697700000003</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>58.805737145087299</v>
       </c>
@@ -995,7 +1002,7 @@
         <v>58.314957556834756</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>63.3360147476196</v>
       </c>
@@ -1031,7 +1038,7 @@
         <v>57.782846093177753</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>54.012489953614597</v>
       </c>
@@ -1068,1153 +1075,1158 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
-        <v>73.441246000000007</v>
+        <v>93.761139999999997</v>
       </c>
       <c r="B1">
-        <v>85.078419999999994</v>
-      </c>
-      <c r="C1" s="3">
-        <v>90.942030000000003</v>
+        <v>91.096535000000003</v>
+      </c>
+      <c r="C1">
+        <v>87.084075999999996</v>
       </c>
       <c r="D1">
-        <v>81.008064000000005</v>
+        <v>83.871499999999997</v>
       </c>
       <c r="E1">
-        <v>99.949929999999995</v>
+        <v>94.335089999999994</v>
       </c>
       <c r="F1">
-        <v>93.834655999999995</v>
-      </c>
-      <c r="G1">
-        <v>100</v>
+        <v>87.255684000000002</v>
+      </c>
+      <c r="G1" s="3">
+        <v>92.478485000000006</v>
       </c>
       <c r="H1">
-        <v>91.735159999999993</v>
+        <v>84.476129999999998</v>
       </c>
       <c r="I1">
-        <v>69.813354000000004</v>
+        <v>84.746055999999996</v>
       </c>
       <c r="J1">
-        <v>95.118110000000001</v>
+        <v>82.046524000000005</v>
       </c>
       <c r="K1" s="1">
         <f>AVERAGE(A1:J1)</f>
-        <v>88.092096999999995</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.115122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>80.204530000000005</v>
+        <v>96.595500000000001</v>
       </c>
       <c r="B2">
-        <v>86.629390000000001</v>
-      </c>
-      <c r="C2" s="3">
-        <v>95.828819999999993</v>
+        <v>93.585526000000002</v>
+      </c>
+      <c r="C2">
+        <v>99.589489999999998</v>
       </c>
       <c r="D2">
-        <v>86.710350000000005</v>
+        <v>95.995760000000004</v>
       </c>
       <c r="E2">
-        <v>97.755480000000006</v>
+        <v>94.971919999999997</v>
       </c>
       <c r="F2">
-        <v>99.306709999999995</v>
-      </c>
-      <c r="G2">
-        <v>92.594440000000006</v>
+        <v>90.687209999999993</v>
+      </c>
+      <c r="G2" s="3">
+        <v>88.050415000000001</v>
       </c>
       <c r="H2">
-        <v>98.972899999999996</v>
+        <v>82.063100000000006</v>
       </c>
       <c r="I2">
-        <v>97.203509999999994</v>
+        <v>94.673569999999998</v>
       </c>
       <c r="J2">
-        <v>82.096664000000004</v>
+        <v>97.912589999999994</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:K19" si="0">AVERAGE(A2:J2)</f>
-        <v>91.730279399999986</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K2:K12" si="0">AVERAGE(A2:J2)</f>
+        <v>93.412508100000011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>99.330240000000003</v>
+        <v>93.935646000000006</v>
       </c>
       <c r="B3">
-        <v>99.530235000000005</v>
-      </c>
-      <c r="C3" s="3">
-        <v>93.534485000000004</v>
+        <v>37.027026999999997</v>
+      </c>
+      <c r="C3">
+        <v>55.981859999999998</v>
       </c>
       <c r="D3">
-        <v>89.740080000000006</v>
+        <v>63.382660000000001</v>
       </c>
       <c r="E3">
-        <v>65.721850000000003</v>
+        <v>44.237050000000004</v>
       </c>
       <c r="F3">
-        <v>88.423150000000007</v>
-      </c>
-      <c r="G3">
-        <v>88.328670000000002</v>
+        <v>64.858345</v>
+      </c>
+      <c r="G3" s="3">
+        <v>49.49174</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>30.094728</v>
       </c>
       <c r="I3">
-        <v>84.862815999999995</v>
+        <v>49.704796000000002</v>
       </c>
       <c r="J3">
-        <v>92.594340000000003</v>
+        <v>52.644683999999998</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" si="0"/>
-        <v>90.206586599999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>54.135853599999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>70.085470000000001</v>
+        <v>74.799139999999994</v>
       </c>
       <c r="B4">
-        <v>90.674610000000001</v>
-      </c>
-      <c r="C4" s="3">
-        <v>96.030640000000005</v>
+        <v>73.891623999999993</v>
+      </c>
+      <c r="C4">
+        <v>79.608940000000004</v>
       </c>
       <c r="D4">
-        <v>74.452160000000006</v>
+        <v>82.736350000000002</v>
       </c>
       <c r="E4">
-        <v>86.159599999999998</v>
+        <v>94.081299999999999</v>
       </c>
       <c r="F4">
-        <v>91.886539999999997</v>
-      </c>
-      <c r="G4">
-        <v>95.214979999999997</v>
+        <v>87.971770000000006</v>
+      </c>
+      <c r="G4" s="3">
+        <v>86.100623999999996</v>
       </c>
       <c r="H4">
-        <v>91.628960000000006</v>
+        <v>31.198553</v>
       </c>
       <c r="I4">
-        <v>91.093649999999997</v>
+        <v>84.244280000000003</v>
       </c>
       <c r="J4">
-        <v>91.141729999999995</v>
+        <v>96.261359999999996</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
-        <v>87.836833999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>79.089394099999993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>99.513490000000004</v>
+        <v>92.503439999999998</v>
       </c>
       <c r="B5">
-        <v>95.620959999999997</v>
-      </c>
-      <c r="C5" s="3">
-        <v>98.779589999999999</v>
+        <v>94.759209999999996</v>
+      </c>
+      <c r="C5">
+        <v>88.603424000000004</v>
       </c>
       <c r="D5">
-        <v>99.591094999999996</v>
+        <v>98.677443999999994</v>
       </c>
       <c r="E5">
-        <v>98.312470000000005</v>
+        <v>98.969825999999998</v>
       </c>
       <c r="F5">
-        <v>95.368650000000002</v>
-      </c>
-      <c r="G5">
-        <v>96.513829999999999</v>
+        <v>86.217950000000002</v>
+      </c>
+      <c r="G5" s="3">
+        <v>86.217950000000002</v>
       </c>
       <c r="H5">
-        <v>90.49391</v>
+        <v>99.925545</v>
       </c>
       <c r="I5">
-        <v>98.580740000000006</v>
+        <v>90.810813999999993</v>
       </c>
       <c r="J5">
-        <v>99.536500000000004</v>
+        <v>98.027760000000001</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
-        <v>97.23112350000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.47133629999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>99.797830000000005</v>
+        <v>51.588590000000003</v>
       </c>
       <c r="B6">
-        <v>95.245440000000002</v>
-      </c>
-      <c r="C6" s="3">
-        <v>82.734116</v>
+        <v>43.718359999999997</v>
+      </c>
+      <c r="C6">
+        <v>35.527439999999999</v>
       </c>
       <c r="D6">
-        <v>99.713393999999994</v>
+        <v>35.274895000000001</v>
       </c>
       <c r="E6">
-        <v>95.250725000000003</v>
+        <v>45.034717999999998</v>
       </c>
       <c r="F6">
-        <v>81.070390000000003</v>
-      </c>
-      <c r="G6">
-        <v>99.166229999999999</v>
+        <v>43.227848000000002</v>
+      </c>
+      <c r="G6" s="3">
+        <v>64.880279999999999</v>
       </c>
       <c r="H6">
-        <v>89.559166000000005</v>
+        <v>27.931929</v>
       </c>
       <c r="I6">
-        <v>72.723929999999996</v>
+        <v>29.694365999999999</v>
       </c>
       <c r="J6">
-        <v>96.774190000000004</v>
+        <v>44.524802999999999</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" si="0"/>
-        <v>91.203541099999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>42.140322900000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>98.344089999999994</v>
+        <v>47.243107000000002</v>
       </c>
       <c r="B7">
-        <v>99.849850000000004</v>
-      </c>
-      <c r="C7" s="3">
-        <v>99.17304</v>
+        <v>53.97287</v>
+      </c>
+      <c r="C7">
+        <v>66.709680000000006</v>
       </c>
       <c r="D7">
-        <v>92.172330000000002</v>
+        <v>64.048676</v>
       </c>
       <c r="E7">
-        <v>92.121679999999998</v>
+        <v>50.079365000000003</v>
       </c>
       <c r="F7">
-        <v>91.824060000000003</v>
-      </c>
-      <c r="G7">
-        <v>95.921199999999999</v>
+        <v>79.020470000000003</v>
+      </c>
+      <c r="G7" s="3">
+        <v>66.203209999999999</v>
       </c>
       <c r="H7">
-        <v>95.469345000000004</v>
+        <v>37.454180000000001</v>
       </c>
       <c r="I7">
-        <v>97.464164999999994</v>
+        <v>33.369185999999999</v>
       </c>
       <c r="J7">
-        <v>97.901899999999998</v>
+        <v>46.326014999999998</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
-        <v>96.024165999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>54.442675900000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>84.787880000000001</v>
+        <v>68.466999999999999</v>
       </c>
       <c r="B8">
-        <v>90.013335999999995</v>
-      </c>
-      <c r="C8" s="3">
-        <v>76.27373</v>
+        <v>74.603589999999997</v>
+      </c>
+      <c r="C8">
+        <v>74.206019999999995</v>
       </c>
       <c r="D8">
-        <v>89.579430000000002</v>
+        <v>64.519170000000003</v>
       </c>
       <c r="E8">
-        <v>91.8035</v>
+        <v>65.938699999999997</v>
       </c>
       <c r="F8">
-        <v>87.032579999999996</v>
-      </c>
-      <c r="G8">
-        <v>76.293723999999997</v>
+        <v>76.673969999999997</v>
+      </c>
+      <c r="G8" s="3">
+        <v>79.523809999999997</v>
       </c>
       <c r="H8">
-        <v>91.111339999999998</v>
+        <v>73.676419999999993</v>
       </c>
       <c r="I8">
-        <v>87.270995999999997</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="J8">
-        <v>86.672004999999999</v>
+        <v>80.522385</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
-        <v>86.083852100000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>73.173106499999989</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>99.174225000000007</v>
+        <v>79.331310000000002</v>
       </c>
       <c r="B9">
-        <v>99.203450000000004</v>
-      </c>
-      <c r="C9" s="3">
-        <v>99.133139999999997</v>
+        <v>74.187730000000002</v>
+      </c>
+      <c r="C9">
+        <v>34.041609999999999</v>
       </c>
       <c r="D9">
-        <v>99.98312</v>
+        <v>81.684979999999996</v>
       </c>
       <c r="E9">
-        <v>90.807379999999995</v>
+        <v>85.215800000000002</v>
       </c>
       <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>92.250860000000003</v>
+        <v>82.126170000000002</v>
+      </c>
+      <c r="G9" s="3">
+        <v>84.923439999999999</v>
       </c>
       <c r="H9">
-        <v>95.992050000000006</v>
+        <v>36.031128000000002</v>
       </c>
       <c r="I9">
-        <v>97.124350000000007</v>
+        <v>83.351585</v>
       </c>
       <c r="J9">
-        <v>99.900890000000004</v>
+        <v>76.400679999999994</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
-        <v>97.356946499999992</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71.729443299999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>96.620819999999995</v>
+        <v>78.733401907611693</v>
       </c>
       <c r="B10">
-        <v>91.765784999999994</v>
-      </c>
-      <c r="C10" s="3">
-        <v>99.673739999999995</v>
+        <v>75.046755189826001</v>
+      </c>
+      <c r="C10">
+        <v>68.966242752945504</v>
       </c>
       <c r="D10">
-        <v>89.81429</v>
+        <v>70.0860295492799</v>
       </c>
       <c r="E10">
-        <v>90.894570000000002</v>
+        <v>74.632971759865299</v>
       </c>
       <c r="F10">
-        <v>82.978729999999999</v>
-      </c>
-      <c r="G10">
-        <v>98.145750000000007</v>
+        <v>78.155975313259702</v>
+      </c>
+      <c r="G10" s="3">
+        <v>81.973536562558394</v>
       </c>
       <c r="H10">
-        <v>89.242744000000002</v>
+        <v>53.829250046755099</v>
       </c>
       <c r="I10">
-        <v>96.193923999999996</v>
+        <v>67.084346362446198</v>
       </c>
       <c r="J10">
-        <v>73.845060000000004</v>
-      </c>
-      <c r="K10" s="1">
-        <f t="shared" si="0"/>
-        <v>90.917541300000011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>76.622405086964605</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="0"/>
+        <v>72.513091453151247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>97.672259999999994</v>
+        <v>77.580541372299194</v>
       </c>
       <c r="B11">
-        <v>98.406750000000002</v>
-      </c>
-      <c r="C11" s="3">
-        <v>99.900695999999996</v>
+        <v>70.760273933410602</v>
+      </c>
+      <c r="C11">
+        <v>69.0391778945922</v>
       </c>
       <c r="D11">
-        <v>89.055980000000005</v>
+        <v>74.465715885162297</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>74.762636423110905</v>
       </c>
       <c r="F11">
-        <v>96.444855000000004</v>
-      </c>
-      <c r="G11">
-        <v>99.903850000000006</v>
+        <v>77.559936046600299</v>
+      </c>
+      <c r="G11" s="3">
+        <v>77.541106939315796</v>
       </c>
       <c r="H11">
-        <v>86.479799999999997</v>
+        <v>55.8724105358123</v>
       </c>
       <c r="I11">
-        <v>99.435559999999995</v>
+        <v>69.354957342147799</v>
       </c>
       <c r="J11">
-        <v>92.321110000000004</v>
-      </c>
-      <c r="K11" s="1">
-        <f t="shared" si="0"/>
-        <v>95.962086099999993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>74.962973594665499</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="0"/>
+        <v>72.189972996711688</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>100</v>
+        <v>72.841536369083698</v>
       </c>
       <c r="B12">
-        <v>97.944500000000005</v>
-      </c>
-      <c r="C12" s="3">
-        <v>100</v>
+        <v>68.282875300151602</v>
+      </c>
+      <c r="C12">
+        <v>62.0770695680689</v>
       </c>
       <c r="D12">
-        <v>99.896209999999996</v>
+        <v>63.141258218840598</v>
       </c>
       <c r="E12">
-        <v>99.896100000000004</v>
+        <v>67.990045385402098</v>
       </c>
       <c r="F12">
-        <v>95.370890000000003</v>
-      </c>
-      <c r="G12">
-        <v>97.556010000000001</v>
+        <v>71.868843935594001</v>
+      </c>
+      <c r="G12" s="3">
+        <v>76.083607597150902</v>
       </c>
       <c r="H12">
-        <v>95.636734000000004</v>
+        <v>44.772488324578198</v>
       </c>
       <c r="I12">
-        <v>99.939499999999995</v>
+        <v>59.398093230528602</v>
       </c>
       <c r="J12">
-        <v>99.689279999999997</v>
-      </c>
-      <c r="K12" s="1">
-        <f t="shared" si="0"/>
-        <v>98.592922399999992</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>98.788539999999998</v>
-      </c>
-      <c r="B13">
-        <v>88.845789999999994</v>
-      </c>
-      <c r="C13" s="3">
-        <v>99.554564999999997</v>
-      </c>
-      <c r="D13">
-        <v>87.87585</v>
-      </c>
-      <c r="E13">
-        <v>97.204300000000003</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
-      <c r="G13">
-        <v>96.308364999999995</v>
-      </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
-      <c r="I13">
-        <v>99.889380000000003</v>
-      </c>
-      <c r="J13">
-        <v>99.875309999999999</v>
-      </c>
-      <c r="K13" s="1">
-        <f t="shared" si="0"/>
-        <v>96.834209999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>98.508849999999995</v>
-      </c>
-      <c r="B14">
-        <v>96.532844999999995</v>
-      </c>
-      <c r="C14" s="3">
-        <v>87.753380000000007</v>
-      </c>
-      <c r="D14">
-        <v>87.542370000000005</v>
-      </c>
-      <c r="E14">
-        <v>99.429659999999998</v>
-      </c>
-      <c r="F14">
-        <v>83.268180000000001</v>
-      </c>
-      <c r="G14">
-        <v>93.630579999999995</v>
-      </c>
-      <c r="H14">
-        <v>94.601770000000002</v>
-      </c>
-      <c r="I14">
-        <v>99.044889999999995</v>
-      </c>
-      <c r="J14">
-        <v>86.499595999999997</v>
-      </c>
-      <c r="K14" s="1">
-        <f t="shared" si="0"/>
-        <v>92.68121210000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>66.686179999999993</v>
-      </c>
-      <c r="B15">
-        <v>53.307270000000003</v>
-      </c>
-      <c r="C15" s="3">
-        <v>69.563249999999996</v>
-      </c>
-      <c r="D15">
-        <v>62.749780000000001</v>
-      </c>
-      <c r="E15">
-        <v>61.275283999999999</v>
-      </c>
-      <c r="F15">
-        <v>53.012050000000002</v>
-      </c>
-      <c r="G15">
-        <v>56.338030000000003</v>
-      </c>
-      <c r="H15">
-        <v>70.867540000000005</v>
-      </c>
-      <c r="I15">
-        <v>68.813010000000006</v>
-      </c>
-      <c r="J15">
-        <v>62.59487</v>
-      </c>
-      <c r="K15" s="1">
-        <f t="shared" si="0"/>
-        <v>62.520726400000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>96.476020000000005</v>
-      </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
-      <c r="C16" s="3">
-        <v>96.590903999999995</v>
-      </c>
-      <c r="D16">
-        <v>95.281189999999995</v>
-      </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-      <c r="F16">
-        <v>98.869349999999997</v>
-      </c>
-      <c r="G16">
-        <v>95.179374999999993</v>
-      </c>
-      <c r="H16">
-        <v>90.84545</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>98.449164999999994</v>
-      </c>
-      <c r="K16" s="1">
-        <f t="shared" si="0"/>
-        <v>97.169145400000005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>87.862328881006405</v>
-      </c>
-      <c r="B17">
-        <v>84.633006336714104</v>
-      </c>
-      <c r="C17" s="3">
-        <v>87.867871196585895</v>
-      </c>
-      <c r="D17">
-        <v>86.362208797502205</v>
-      </c>
-      <c r="E17">
-        <v>86.243972731807304</v>
-      </c>
-      <c r="F17">
-        <v>83.022039941620903</v>
-      </c>
-      <c r="G17">
-        <v>85.414472833416397</v>
-      </c>
-      <c r="H17">
-        <v>89.43634650557</v>
-      </c>
-      <c r="I17">
-        <v>86.6984426093221</v>
-      </c>
-      <c r="J17">
-        <v>86.072160948844399</v>
-      </c>
-      <c r="K17" s="3">
-        <f t="shared" si="0"/>
-        <v>86.361285078238978</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>91.214478015899601</v>
-      </c>
-      <c r="B18">
-        <v>91.790539026260305</v>
-      </c>
-      <c r="C18" s="3">
-        <v>92.841631174087496</v>
-      </c>
-      <c r="D18">
-        <v>89.072859287261906</v>
-      </c>
-      <c r="E18">
-        <v>91.661405563354407</v>
-      </c>
-      <c r="F18">
-        <v>89.918172359466496</v>
-      </c>
-      <c r="G18">
-        <v>92.084121704101506</v>
-      </c>
-      <c r="H18">
-        <v>92.039805650711003</v>
-      </c>
-      <c r="I18">
-        <v>91.215860843658405</v>
-      </c>
-      <c r="J18">
-        <v>90.938174724578801</v>
-      </c>
-      <c r="K18" s="3">
-        <f t="shared" si="0"/>
-        <v>91.277704834938021</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>86.515882762251593</v>
-      </c>
-      <c r="B19">
-        <v>83.032079660666398</v>
-      </c>
-      <c r="C19" s="3">
-        <v>86.475461355417707</v>
-      </c>
-      <c r="D19">
-        <v>84.916331261410505</v>
-      </c>
-      <c r="E19">
-        <v>84.766143271572503</v>
-      </c>
-      <c r="F19">
-        <v>81.254030297390202</v>
-      </c>
-      <c r="G19">
-        <v>83.762302424336198</v>
-      </c>
-      <c r="H19">
-        <v>88.275670312937507</v>
-      </c>
-      <c r="I19">
-        <v>85.236516378222504</v>
-      </c>
-      <c r="J19">
-        <v>84.554386593805404</v>
-      </c>
-      <c r="K19" s="3">
-        <f t="shared" si="0"/>
-        <v>84.878880431801051</v>
+        <v>70.444924154162194</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="0"/>
+        <v>65.69007420835608</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
-        <v>93.761139999999997</v>
+        <v>73.441246000000007</v>
       </c>
       <c r="B1">
-        <v>91.096535000000003</v>
-      </c>
-      <c r="C1">
-        <v>87.084075999999996</v>
+        <v>85.078419999999994</v>
+      </c>
+      <c r="C1" s="3">
+        <v>90.942030000000003</v>
       </c>
       <c r="D1">
-        <v>83.871499999999997</v>
+        <v>81.008064000000005</v>
       </c>
       <c r="E1">
-        <v>94.335089999999994</v>
+        <v>99.949929999999995</v>
       </c>
       <c r="F1">
-        <v>87.255684000000002</v>
-      </c>
-      <c r="G1" s="3">
-        <v>92.478485000000006</v>
+        <v>93.834655999999995</v>
+      </c>
+      <c r="G1">
+        <v>100</v>
       </c>
       <c r="H1">
-        <v>84.476129999999998</v>
+        <v>91.735159999999993</v>
       </c>
       <c r="I1">
-        <v>84.746055999999996</v>
+        <v>69.813354000000004</v>
       </c>
       <c r="J1">
-        <v>82.046524000000005</v>
+        <v>95.118110000000001</v>
       </c>
       <c r="K1" s="1">
         <f>AVERAGE(A1:J1)</f>
-        <v>88.115122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.092096999999995</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>96.595500000000001</v>
+        <v>80.204530000000005</v>
       </c>
       <c r="B2">
-        <v>93.585526000000002</v>
-      </c>
-      <c r="C2">
-        <v>99.589489999999998</v>
+        <v>86.629390000000001</v>
+      </c>
+      <c r="C2" s="3">
+        <v>95.828819999999993</v>
       </c>
       <c r="D2">
-        <v>95.995760000000004</v>
+        <v>86.710350000000005</v>
       </c>
       <c r="E2">
-        <v>94.971919999999997</v>
+        <v>97.755480000000006</v>
       </c>
       <c r="F2">
-        <v>90.687209999999993</v>
-      </c>
-      <c r="G2" s="3">
-        <v>88.050415000000001</v>
+        <v>99.306709999999995</v>
+      </c>
+      <c r="G2">
+        <v>92.594440000000006</v>
       </c>
       <c r="H2">
-        <v>82.063100000000006</v>
+        <v>98.972899999999996</v>
       </c>
       <c r="I2">
-        <v>94.673569999999998</v>
+        <v>97.203509999999994</v>
       </c>
       <c r="J2">
-        <v>97.912589999999994</v>
+        <v>82.096664000000004</v>
       </c>
       <c r="K2" s="1">
-        <f t="shared" ref="K2:K12" si="0">AVERAGE(A2:J2)</f>
-        <v>93.412508100000011</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="K2:K19" si="0">AVERAGE(A2:J2)</f>
+        <v>91.730279399999986</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>93.935646000000006</v>
+        <v>99.330240000000003</v>
       </c>
       <c r="B3">
-        <v>37.027026999999997</v>
-      </c>
-      <c r="C3">
-        <v>55.981859999999998</v>
+        <v>99.530235000000005</v>
+      </c>
+      <c r="C3" s="3">
+        <v>93.534485000000004</v>
       </c>
       <c r="D3">
-        <v>63.382660000000001</v>
+        <v>89.740080000000006</v>
       </c>
       <c r="E3">
-        <v>44.237050000000004</v>
+        <v>65.721850000000003</v>
       </c>
       <c r="F3">
-        <v>64.858345</v>
-      </c>
-      <c r="G3" s="3">
-        <v>49.49174</v>
+        <v>88.423150000000007</v>
+      </c>
+      <c r="G3">
+        <v>88.328670000000002</v>
       </c>
       <c r="H3">
-        <v>30.094728</v>
+        <v>100</v>
       </c>
       <c r="I3">
-        <v>49.704796000000002</v>
+        <v>84.862815999999995</v>
       </c>
       <c r="J3">
-        <v>52.644683999999998</v>
+        <v>92.594340000000003</v>
       </c>
       <c r="K3" s="1">
         <f t="shared" si="0"/>
-        <v>54.135853599999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90.206586599999994</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>74.799139999999994</v>
+        <v>70.085470000000001</v>
       </c>
       <c r="B4">
-        <v>73.891623999999993</v>
-      </c>
-      <c r="C4">
-        <v>79.608940000000004</v>
+        <v>90.674610000000001</v>
+      </c>
+      <c r="C4" s="3">
+        <v>96.030640000000005</v>
       </c>
       <c r="D4">
-        <v>82.736350000000002</v>
+        <v>74.452160000000006</v>
       </c>
       <c r="E4">
-        <v>94.081299999999999</v>
+        <v>86.159599999999998</v>
       </c>
       <c r="F4">
-        <v>87.971770000000006</v>
-      </c>
-      <c r="G4" s="3">
-        <v>86.100623999999996</v>
+        <v>91.886539999999997</v>
+      </c>
+      <c r="G4">
+        <v>95.214979999999997</v>
       </c>
       <c r="H4">
-        <v>31.198553</v>
+        <v>91.628960000000006</v>
       </c>
       <c r="I4">
-        <v>84.244280000000003</v>
+        <v>91.093649999999997</v>
       </c>
       <c r="J4">
-        <v>96.261359999999996</v>
+        <v>91.141729999999995</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" si="0"/>
-        <v>79.089394099999993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>87.836833999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>92.503439999999998</v>
+        <v>99.513490000000004</v>
       </c>
       <c r="B5">
-        <v>94.759209999999996</v>
-      </c>
-      <c r="C5">
-        <v>88.603424000000004</v>
+        <v>95.620959999999997</v>
+      </c>
+      <c r="C5" s="3">
+        <v>98.779589999999999</v>
       </c>
       <c r="D5">
-        <v>98.677443999999994</v>
+        <v>99.591094999999996</v>
       </c>
       <c r="E5">
-        <v>98.969825999999998</v>
+        <v>98.312470000000005</v>
       </c>
       <c r="F5">
-        <v>86.217950000000002</v>
-      </c>
-      <c r="G5" s="3">
-        <v>86.217950000000002</v>
+        <v>95.368650000000002</v>
+      </c>
+      <c r="G5">
+        <v>96.513829999999999</v>
       </c>
       <c r="H5">
-        <v>99.925545</v>
+        <v>90.49391</v>
       </c>
       <c r="I5">
-        <v>90.810813999999993</v>
+        <v>98.580740000000006</v>
       </c>
       <c r="J5">
-        <v>98.027760000000001</v>
+        <v>99.536500000000004</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" si="0"/>
-        <v>93.47133629999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97.23112350000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>51.588590000000003</v>
+        <v>99.797830000000005</v>
       </c>
       <c r="B6">
-        <v>43.718359999999997</v>
-      </c>
-      <c r="C6">
-        <v>35.527439999999999</v>
+        <v>95.245440000000002</v>
+      </c>
+      <c r="C6" s="3">
+        <v>82.734116</v>
       </c>
       <c r="D6">
-        <v>35.274895000000001</v>
+        <v>99.713393999999994</v>
       </c>
       <c r="E6">
-        <v>45.034717999999998</v>
+        <v>95.250725000000003</v>
       </c>
       <c r="F6">
-        <v>43.227848000000002</v>
-      </c>
-      <c r="G6" s="3">
-        <v>64.880279999999999</v>
+        <v>81.070390000000003</v>
+      </c>
+      <c r="G6">
+        <v>99.166229999999999</v>
       </c>
       <c r="H6">
-        <v>27.931929</v>
+        <v>89.559166000000005</v>
       </c>
       <c r="I6">
-        <v>29.694365999999999</v>
+        <v>72.723929999999996</v>
       </c>
       <c r="J6">
-        <v>44.524802999999999</v>
+        <v>96.774190000000004</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" si="0"/>
-        <v>42.140322900000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>91.203541099999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>47.243107000000002</v>
+        <v>98.344089999999994</v>
       </c>
       <c r="B7">
-        <v>53.97287</v>
-      </c>
-      <c r="C7">
-        <v>66.709680000000006</v>
+        <v>99.849850000000004</v>
+      </c>
+      <c r="C7" s="3">
+        <v>99.17304</v>
       </c>
       <c r="D7">
-        <v>64.048676</v>
+        <v>92.172330000000002</v>
       </c>
       <c r="E7">
-        <v>50.079365000000003</v>
+        <v>92.121679999999998</v>
       </c>
       <c r="F7">
-        <v>79.020470000000003</v>
-      </c>
-      <c r="G7" s="3">
-        <v>66.203209999999999</v>
+        <v>91.824060000000003</v>
+      </c>
+      <c r="G7">
+        <v>95.921199999999999</v>
       </c>
       <c r="H7">
-        <v>37.454180000000001</v>
+        <v>95.469345000000004</v>
       </c>
       <c r="I7">
-        <v>33.369185999999999</v>
+        <v>97.464164999999994</v>
       </c>
       <c r="J7">
-        <v>46.326014999999998</v>
+        <v>97.901899999999998</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" si="0"/>
-        <v>54.442675900000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>96.024165999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>68.466999999999999</v>
+        <v>84.787880000000001</v>
       </c>
       <c r="B8">
-        <v>74.603589999999997</v>
-      </c>
-      <c r="C8">
-        <v>74.206019999999995</v>
+        <v>90.013335999999995</v>
+      </c>
+      <c r="C8" s="3">
+        <v>76.27373</v>
       </c>
       <c r="D8">
-        <v>64.519170000000003</v>
+        <v>89.579430000000002</v>
       </c>
       <c r="E8">
-        <v>65.938699999999997</v>
+        <v>91.8035</v>
       </c>
       <c r="F8">
-        <v>76.673969999999997</v>
-      </c>
-      <c r="G8" s="3">
-        <v>79.523809999999997</v>
+        <v>87.032579999999996</v>
+      </c>
+      <c r="G8">
+        <v>76.293723999999997</v>
       </c>
       <c r="H8">
-        <v>73.676419999999993</v>
+        <v>91.111339999999998</v>
       </c>
       <c r="I8">
-        <v>73.599999999999994</v>
+        <v>87.270995999999997</v>
       </c>
       <c r="J8">
-        <v>80.522385</v>
+        <v>86.672004999999999</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" si="0"/>
-        <v>73.173106499999989</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>86.083852100000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>79.331310000000002</v>
+        <v>99.174225000000007</v>
       </c>
       <c r="B9">
-        <v>74.187730000000002</v>
-      </c>
-      <c r="C9">
-        <v>34.041609999999999</v>
+        <v>99.203450000000004</v>
+      </c>
+      <c r="C9" s="3">
+        <v>99.133139999999997</v>
       </c>
       <c r="D9">
-        <v>81.684979999999996</v>
+        <v>99.98312</v>
       </c>
       <c r="E9">
-        <v>85.215800000000002</v>
+        <v>90.807379999999995</v>
       </c>
       <c r="F9">
-        <v>82.126170000000002</v>
-      </c>
-      <c r="G9" s="3">
-        <v>84.923439999999999</v>
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>92.250860000000003</v>
       </c>
       <c r="H9">
-        <v>36.031128000000002</v>
+        <v>95.992050000000006</v>
       </c>
       <c r="I9">
-        <v>83.351585</v>
+        <v>97.124350000000007</v>
       </c>
       <c r="J9">
-        <v>76.400679999999994</v>
+        <v>99.900890000000004</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" si="0"/>
-        <v>71.729443299999986</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97.356946499999992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>78.733401907611693</v>
+        <v>96.620819999999995</v>
       </c>
       <c r="B10">
-        <v>75.046755189826001</v>
-      </c>
-      <c r="C10">
-        <v>68.966242752945504</v>
+        <v>91.765784999999994</v>
+      </c>
+      <c r="C10" s="3">
+        <v>99.673739999999995</v>
       </c>
       <c r="D10">
-        <v>70.0860295492799</v>
+        <v>89.81429</v>
       </c>
       <c r="E10">
-        <v>74.632971759865299</v>
+        <v>90.894570000000002</v>
       </c>
       <c r="F10">
-        <v>78.155975313259702</v>
-      </c>
-      <c r="G10" s="3">
-        <v>81.973536562558394</v>
+        <v>82.978729999999999</v>
+      </c>
+      <c r="G10">
+        <v>98.145750000000007</v>
       </c>
       <c r="H10">
-        <v>53.829250046755099</v>
+        <v>89.242744000000002</v>
       </c>
       <c r="I10">
-        <v>67.084346362446198</v>
+        <v>96.193923999999996</v>
       </c>
       <c r="J10">
-        <v>76.622405086964605</v>
-      </c>
-      <c r="K10" s="3">
-        <f t="shared" si="0"/>
-        <v>72.513091453151247</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>73.845060000000004</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>90.917541300000011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>77.580541372299194</v>
+        <v>97.672259999999994</v>
       </c>
       <c r="B11">
-        <v>70.760273933410602</v>
-      </c>
-      <c r="C11">
-        <v>69.0391778945922</v>
+        <v>98.406750000000002</v>
+      </c>
+      <c r="C11" s="3">
+        <v>99.900695999999996</v>
       </c>
       <c r="D11">
-        <v>74.465715885162297</v>
+        <v>89.055980000000005</v>
       </c>
       <c r="E11">
-        <v>74.762636423110905</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>77.559936046600299</v>
-      </c>
-      <c r="G11" s="3">
-        <v>77.541106939315796</v>
+        <v>96.444855000000004</v>
+      </c>
+      <c r="G11">
+        <v>99.903850000000006</v>
       </c>
       <c r="H11">
-        <v>55.8724105358123</v>
+        <v>86.479799999999997</v>
       </c>
       <c r="I11">
-        <v>69.354957342147799</v>
+        <v>99.435559999999995</v>
       </c>
       <c r="J11">
-        <v>74.962973594665499</v>
-      </c>
-      <c r="K11" s="3">
-        <f t="shared" si="0"/>
-        <v>72.189972996711688</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>92.321110000000004</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>95.962086099999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>72.841536369083698</v>
+        <v>100</v>
       </c>
       <c r="B12">
-        <v>68.282875300151602</v>
-      </c>
-      <c r="C12">
-        <v>62.0770695680689</v>
+        <v>97.944500000000005</v>
+      </c>
+      <c r="C12" s="3">
+        <v>100</v>
       </c>
       <c r="D12">
-        <v>63.141258218840598</v>
+        <v>99.896209999999996</v>
       </c>
       <c r="E12">
-        <v>67.990045385402098</v>
+        <v>99.896100000000004</v>
       </c>
       <c r="F12">
-        <v>71.868843935594001</v>
-      </c>
-      <c r="G12" s="3">
-        <v>76.083607597150902</v>
+        <v>95.370890000000003</v>
+      </c>
+      <c r="G12">
+        <v>97.556010000000001</v>
       </c>
       <c r="H12">
-        <v>44.772488324578198</v>
+        <v>95.636734000000004</v>
       </c>
       <c r="I12">
-        <v>59.398093230528602</v>
+        <v>99.939499999999995</v>
       </c>
       <c r="J12">
-        <v>70.444924154162194</v>
-      </c>
-      <c r="K12" s="3">
-        <f t="shared" si="0"/>
-        <v>65.69007420835608</v>
+        <v>99.689279999999997</v>
+      </c>
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>98.592922399999992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>98.788539999999998</v>
+      </c>
+      <c r="B13">
+        <v>88.845789999999994</v>
+      </c>
+      <c r="C13" s="3">
+        <v>99.554564999999997</v>
+      </c>
+      <c r="D13">
+        <v>87.87585</v>
+      </c>
+      <c r="E13">
+        <v>97.204300000000003</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>96.308364999999995</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>99.889380000000003</v>
+      </c>
+      <c r="J13">
+        <v>99.875309999999999</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>96.834209999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>98.508849999999995</v>
+      </c>
+      <c r="B14">
+        <v>96.532844999999995</v>
+      </c>
+      <c r="C14" s="3">
+        <v>87.753380000000007</v>
+      </c>
+      <c r="D14">
+        <v>87.542370000000005</v>
+      </c>
+      <c r="E14">
+        <v>99.429659999999998</v>
+      </c>
+      <c r="F14">
+        <v>83.268180000000001</v>
+      </c>
+      <c r="G14">
+        <v>93.630579999999995</v>
+      </c>
+      <c r="H14">
+        <v>94.601770000000002</v>
+      </c>
+      <c r="I14">
+        <v>99.044889999999995</v>
+      </c>
+      <c r="J14">
+        <v>86.499595999999997</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>92.68121210000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>66.686179999999993</v>
+      </c>
+      <c r="B15">
+        <v>53.307270000000003</v>
+      </c>
+      <c r="C15" s="3">
+        <v>69.563249999999996</v>
+      </c>
+      <c r="D15">
+        <v>62.749780000000001</v>
+      </c>
+      <c r="E15">
+        <v>61.275283999999999</v>
+      </c>
+      <c r="F15">
+        <v>53.012050000000002</v>
+      </c>
+      <c r="G15">
+        <v>56.338030000000003</v>
+      </c>
+      <c r="H15">
+        <v>70.867540000000005</v>
+      </c>
+      <c r="I15">
+        <v>68.813010000000006</v>
+      </c>
+      <c r="J15">
+        <v>62.59487</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>62.520726400000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>96.476020000000005</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>96.590903999999995</v>
+      </c>
+      <c r="D16">
+        <v>95.281189999999995</v>
+      </c>
+      <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>98.869349999999997</v>
+      </c>
+      <c r="G16">
+        <v>95.179374999999993</v>
+      </c>
+      <c r="H16">
+        <v>90.84545</v>
+      </c>
+      <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
+        <v>98.449164999999994</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
+        <v>97.169145400000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>87.862328881006405</v>
+      </c>
+      <c r="B17">
+        <v>84.633006336714104</v>
+      </c>
+      <c r="C17" s="3">
+        <v>87.867871196585895</v>
+      </c>
+      <c r="D17">
+        <v>86.362208797502205</v>
+      </c>
+      <c r="E17">
+        <v>86.243972731807304</v>
+      </c>
+      <c r="F17">
+        <v>83.022039941620903</v>
+      </c>
+      <c r="G17">
+        <v>85.414472833416397</v>
+      </c>
+      <c r="H17">
+        <v>89.43634650557</v>
+      </c>
+      <c r="I17">
+        <v>86.6984426093221</v>
+      </c>
+      <c r="J17">
+        <v>86.072160948844399</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="0"/>
+        <v>86.361285078238978</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>91.214478015899601</v>
+      </c>
+      <c r="B18">
+        <v>91.790539026260305</v>
+      </c>
+      <c r="C18" s="3">
+        <v>92.841631174087496</v>
+      </c>
+      <c r="D18">
+        <v>89.072859287261906</v>
+      </c>
+      <c r="E18">
+        <v>91.661405563354407</v>
+      </c>
+      <c r="F18">
+        <v>89.918172359466496</v>
+      </c>
+      <c r="G18">
+        <v>92.084121704101506</v>
+      </c>
+      <c r="H18">
+        <v>92.039805650711003</v>
+      </c>
+      <c r="I18">
+        <v>91.215860843658405</v>
+      </c>
+      <c r="J18">
+        <v>90.938174724578801</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="0"/>
+        <v>91.277704834938021</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>86.515882762251593</v>
+      </c>
+      <c r="B19">
+        <v>83.032079660666398</v>
+      </c>
+      <c r="C19" s="3">
+        <v>86.475461355417707</v>
+      </c>
+      <c r="D19">
+        <v>84.916331261410505</v>
+      </c>
+      <c r="E19">
+        <v>84.766143271572503</v>
+      </c>
+      <c r="F19">
+        <v>81.254030297390202</v>
+      </c>
+      <c r="G19">
+        <v>83.762302424336198</v>
+      </c>
+      <c r="H19">
+        <v>88.275670312937507</v>
+      </c>
+      <c r="I19">
+        <v>85.236516378222504</v>
+      </c>
+      <c r="J19">
+        <v>84.554386593805404</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="0"/>
+        <v>84.878880431801051</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>93.530265999999997</v>
       </c>
@@ -2238,7 +2250,7 @@
         <v>90.830305999999993</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>86.256029999999996</v>
       </c>
@@ -2262,7 +2274,7 @@
         <v>89.393990833333348</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>58.17745</v>
       </c>
@@ -2286,7 +2298,7 @@
         <v>65.485466833333334</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>36.561714000000002</v>
       </c>
@@ -2310,7 +2322,7 @@
         <v>47.366563166666673</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>95.675520000000006</v>
       </c>
@@ -2334,7 +2346,7 @@
         <v>90.749449999999982</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>80.677660000000003</v>
       </c>
@@ -2358,7 +2370,7 @@
         <v>69.516127166666664</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>83.844130000000007</v>
       </c>
@@ -2382,7 +2394,7 @@
         <v>72.996705000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>93.473724000000004</v>
       </c>
@@ -2406,7 +2418,7 @@
         <v>84.666268833333334</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>53.983739999999997</v>
       </c>
@@ -2430,7 +2442,7 @@
         <v>67.979109666666673</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>80.900736094777599</v>
       </c>
@@ -2454,7 +2466,7 @@
         <v>78.496450193823733</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>75.797802209854098</v>
       </c>
@@ -2478,7 +2490,7 @@
         <v>75.442663828531863</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>76.120236755149094</v>
       </c>
@@ -2503,15 +2515,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>